--- a/Verslag/Taakverdeling.xlsx
+++ b/Verslag/Taakverdeling.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thomasmore365-my.sharepoint.com/personal/r1093663_student_thomasmore_be/Documents/PE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thomasmore365-my.sharepoint.com/personal/r1093663_student_thomasmore_be/Documents/PE/Verslag/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{2D2085BE-558B-427A-85D5-2DCDA72DFB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD4FF656-2E1B-4367-8C65-F828022278E0}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{2D2085BE-558B-427A-85D5-2DCDA72DFB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCD4C639-31ED-4070-8D5A-C3CF676AF40A}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2280" yWindow="2280" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Taakverdeling" sheetId="1" r:id="rId1"/>
@@ -79,13 +79,13 @@
     <t>3-4 Weken</t>
   </si>
   <si>
-    <t>30 uur</t>
-  </si>
-  <si>
     <t>22-26 uur</t>
   </si>
   <si>
     <t>25-27 uur</t>
+  </si>
+  <si>
+    <t>35 uur</t>
   </si>
 </sst>
 </file>
@@ -193,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -235,10 +235,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -251,6 +250,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -539,18 +542,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="17.9296875" customWidth="1"/>
+    <col min="4" max="4" width="17.90625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
         <v>13</v>
       </c>
@@ -562,8 +565,8 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
@@ -578,8 +581,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="5" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -593,7 +596,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
@@ -607,7 +610,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
@@ -621,7 +624,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>3</v>
       </c>
@@ -632,10 +635,10 @@
         <v>2</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>4</v>
       </c>
@@ -649,7 +652,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>5</v>
       </c>
@@ -660,10 +663,10 @@
         <v>3</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
@@ -677,7 +680,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>7</v>
       </c>
@@ -688,14 +691,10 @@
         <v>1</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:B3"/>
@@ -850,18 +849,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -883,14 +882,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{330C63DD-040C-4640-ABB6-3971B3FDF04C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{029BC496-1C69-4CC4-B0C9-F271F5A3A45A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -904,4 +895,12 @@
     <ds:schemaRef ds:uri="187ed867-fc70-448b-aee7-aa48c4959a25"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{330C63DD-040C-4640-ABB6-3971B3FDF04C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>